--- a/Du an PTN cao hoc Hoa hoc/Bang 1 - danh muc thiet bi va gia.xlsx
+++ b/Du an PTN cao hoc Hoa hoc/Bang 1 - danh muc thiet bi va gia.xlsx
@@ -1085,12 +1085,7 @@
       <c r="E31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>(*) Đơn giá ước lượng, chưa có báo giá.</t>
-        </is>
-      </c>
+      <c r="B32" s="9" t="n"/>
       <c r="D32" s="8" t="n"/>
       <c r="E32" s="8" t="n"/>
     </row>

--- a/Du an PTN cao hoc Hoa hoc/Bang 1 - danh muc thiet bi va gia.xlsx
+++ b/Du an PTN cao hoc Hoa hoc/Bang 1 - danh muc thiet bi va gia.xlsx
@@ -469,7 +469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -776,7 +776,7 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="4" t="n">
         <v>900000000</v>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D19" s="4" t="n">
         <v>500000000</v>
@@ -872,14 +872,14 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Máy quang phổ UV-Vis hai chùm tia</t>
+          <t>Lò nung buồng 1.100 °C</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>200000000</v>
+        <v>323090000</v>
       </c>
       <c r="E20" s="4">
         <f>C20*D20</f>
@@ -892,14 +892,14 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Máy sắc ký khí (FID, TCD)</t>
+          <t>Tủ đựng hóa chất có lọc than hoạt tính</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>2200000000</v>
+        <v>90000000</v>
       </c>
       <c r="E21" s="4">
         <f>C21*D21</f>
@@ -912,14 +912,14 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Máy đo kích thước hạt và thế zeta</t>
+          <t>Máy đo pH để bàn</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>4389940000</v>
+        <v>35360000</v>
       </c>
       <c r="E22" s="4">
         <f>C22*D22</f>
@@ -932,14 +932,14 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Hệ phân tích nhiệt trọng lượng ghép nối FTIR (TGA-FTIR)</t>
+          <t>Máy khuấy cơ</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3200000000</v>
+        <v>52700000</v>
       </c>
       <c r="E23" s="4">
         <f>C23*D23</f>
@@ -952,14 +952,14 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Máy quang phổ hấp thụ nguyên tử (AAS) ngọn lửa</t>
+          <t>Máy phân tích độ ẩm</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1500000000</v>
+        <v>27500000</v>
       </c>
       <c r="E24" s="4">
         <f>C24*D24</f>
@@ -972,14 +972,14 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Máy thử kéo vạn năng</t>
+          <t>Bể điều nhiệt 45 L</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>800000000</v>
+        <v>60040000</v>
       </c>
       <c r="E25" s="4">
         <f>C25*D25</f>
@@ -992,14 +992,14 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Máy đo điện trở mặt 4 mũi dò</t>
+          <t>Máy quang phổ UV-Vis hai chùm tia</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>300000000</v>
+        <v>200000000</v>
       </c>
       <c r="E26" s="4">
         <f>C26*D26</f>
@@ -1012,14 +1012,14 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Máy quang phổ huỳnh quang</t>
+          <t>Máy sắc ký khí (FID, TCD)</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>1500000000</v>
+        <v>2200000000</v>
       </c>
       <c r="E27" s="4">
         <f>C27*D27</f>
@@ -1032,14 +1032,14 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Hệ đo độ hòa tan 8 vị trí kèm lấy mẫu tự động</t>
+          <t>Máy phân tích nhiệt trọng lượng (TGA)</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3000000000</v>
+        <v>1300000000</v>
       </c>
       <c r="E28" s="4">
         <f>C28*D28</f>
@@ -1052,14 +1052,14 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Máy đo điện hóa đa kênh (potentiostat/galvanostat)</t>
+          <t>Máy quang phổ hấp thụ nguyên tử (AAS) ngọn lửa</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>500000000</v>
+        <v>1500000000</v>
       </c>
       <c r="E29" s="4">
         <f>C29*D29</f>
@@ -1067,27 +1067,98 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr"/>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="A30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Máy thử kéo vạn năng</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>800000000</v>
+      </c>
+      <c r="E30" s="4">
+        <f>C30*D30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Máy đo điện trở mặt 4 mũi dò</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="4" t="n">
+        <v>300000000</v>
+      </c>
+      <c r="E31" s="4">
+        <f>C31*D31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Máy quang phổ huỳnh quang</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>1500000000</v>
+      </c>
+      <c r="E32" s="4">
+        <f>C32*D32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Máy đo điện hóa đa kênh (potentiostat/galvanostat)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>500000000</v>
+      </c>
+      <c r="E33" s="4">
+        <f>C33*D33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>TỔNG CỘNG</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="7" t="inlineStr"/>
-      <c r="E30" s="7">
-        <f>SUM(E2:E29)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="B32" s="9" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="7" t="inlineStr"/>
+      <c r="E34" s="7">
+        <f>SUM(E2:E33)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
